--- a/rmonize/data_proc_elem/DPE_IDEFICS_P1.xlsx
+++ b/rmonize/data_proc_elem/DPE_IDEFICS_P1.xlsx
@@ -437,7 +437,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ID_cohort</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -492,12 +492,21 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>case_when</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>case_when(_x000D_
+  sex_child == 1 ~ 1L, _x000D_
+  sex_child == 2 ~ 2L, _x000D_
+  TRUE ~ NA_integer__x000D_
+)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>FS: there are categories 0,3 and 9 which are not male or female</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -597,7 +606,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>recode(0=0;1=1;2=2;3=3;4=4;5=5;6=7;)</t>
+          <t>recode(0=0;1=1;2=2;3=3;4=4;5=7;6=8;9=9)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>FS: addresses correct ISCED-1997 levels</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -647,7 +661,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(4 * phys_activ + 1.5 * leis_activ) / 7</t>
+          <t>6.17 * (phys_activ + leis_activ) / 7</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>The average MET value of children between 6 to 15years was determined according to NCCOR Compendium.METy Values (Smoothed) – View All Categories - NCCOR Youth Compendium of Physical Activities</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -782,8 +801,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>energy_kcal (foodcoll_calc_alldays_bls)_x000D_
-energy_kcal_day (Core)</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -794,6 +812,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>To be generated by the DHO</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -833,7 +856,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>POTATOES_TUB_01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -848,7 +871,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SACANA FGS D19 "Potatoes and other starchy vegetables"</t>
+          <t>SACANA FGS D19 "Potatoes and other starchy vegetables" + SACANA FGS 19a " Potatoes cooked (not deep fried)" + SACANA FGS 19b " Potatoes cooked (deep fried)" + (Proportion of SACANA FGS L47 "Based on potatoes")</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -888,22 +911,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D19a; D19b;L47</t>
+          <t>POTATOES_0101</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>D19a + D19b + (weighting*L47)</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SACANA FGS D19a " Potatoes cooked (not deep fried) " + SACANA FGS 19b " Potatoes cooked (deep fried) " + (Gewichtung* SACANA FGS L47 "Based on potatoes")</t>
+          <t>SACANA FGS D19 "Potatoes and other starchy vegetables" + SACANA FGS 19a " Potatoes cooked (not deep fried)" + SACANA FGS 19b " Potatoes cooked (deep fried)" + (Gewichtung* SACANA FGS L47 "Based on potatoes")</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -913,7 +936,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -993,7 +1016,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>VEGETABLES_02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1008,7 +1031,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SACANA FGS D18 vegetables n.s.</t>
+          <t>sum of all items related to vegetables (as indicated in separate Excel sheet)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1048,27 +1071,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>LEAFYVEG_0201</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>(Proportion of D18a "Vegetables raw") + (Proportion of D18b "Vegetables cooked or preserved (not deep fried)" + (Proportion of D18c"Vegetable cooked (deep fried) "</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -1098,27 +1126,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>FRUITINGVEG_0202</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>(Proportion of D18a "Vegetables raw") + (Proportion of D18b "Vegetables cooked or preserved (not deep fried)"</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -1148,27 +1181,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>ROOTVEG_0203</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>(Proportion of D18a "Vegetables raw") + (Proportion of D18b "Vegetables cooked or preserved (not deep fried)"</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -1198,27 +1236,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>CABBAGE_0204</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>(Proportion of D18a "Vegetables raw") + (Proportion of D18b "Vegetables cooked or preserved (not deep fried)"</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -1248,27 +1291,32 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>MUSHROOMS_0205</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Proportion of D18b</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -1298,27 +1346,32 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>GRAINPODVEG_0206</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>(Proportion of D18a "Vegetables raw") + (Proportion of D18b "Vegetables cooked or preserved (not deep fried)"</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -1348,27 +1401,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>ONION_GARLIC_0207</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Proportion of D18a</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -1398,27 +1456,32 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>STALKVEG_0208</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>(Proportion of D18a "Vegetables raw") + (Proportion of D18b "Vegetables cooked or preserved (not deep fried)"</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1511,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>L44c</t>
+          <t>MIXEDVEG_0209</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1463,7 +1526,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SACANA FGS L44c "Mixed salad"</t>
+          <t>(Proportion of D18b "Vegetables cooked or preserved (not deep fried) + "SACANA FGS L44c "Mixed salad"</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1503,22 +1566,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>D17;L44;L46a</t>
+          <t>LEGUMES_TOT_03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>D17 + (weighting *L44) + (weighting*L46a)</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SACANA FGS D17 Pulses n.s. + (Gewichtung*L44 "Legumes/Vegs n.s.") + (Gewichtung*L46a "Fish and vegetables/legumes")</t>
+          <t>SACANA FGS D17 Pulses n.s. + (Proportion of L44 "Legumes/Vegs n.s.")</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1528,7 +1591,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1671,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>FRUITS_TOT_04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1623,7 +1686,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SACANA FGS D20 "Fruits n.s."</t>
+          <t>SACANA FGS D20 "Fruits n.s." + SACANA FGS D20a "Fresh fruits" + SACANA FGS 16a "Nuts and seeds"</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1663,7 +1726,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>D20a</t>
+          <t>FRUITS_0401</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1718,7 +1781,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>D16a</t>
+          <t>NUTS_SEEDS_0402</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1773,27 +1836,32 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>MIXEDFRUITS_0403</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>SACANA FGS D20 "Fruits n.s." + SACANA FGS D20b</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -1823,32 +1891,32 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>D16b</t>
+          <t>OLIVES_0404</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Weighting*D16b</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SACANA FGS D16b "Olives and avocados" (Gewichtung für Oliven?)</t>
+          <t>SACANA FGS D16b "Olives and avocados" (Only proportion of olives)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1946,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>DAIRY_05</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1893,7 +1961,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SACANA FGS J "Dairy and similar"</t>
+          <t>Sum of all items in SACANA FGS J37 to J39c and K40b</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1933,17 +2001,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>J37a;J37b</t>
+          <t>MILK_0501</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>J37a + J37b</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1958,7 +2026,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2056,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>J37c</t>
+          <t>MILKBEV_0502</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2043,17 +2111,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>J37d;J37e;J37f;J37g</t>
+          <t>YOGURT_0503</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>J37d+J37e+J37f+J37g</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2068,7 +2136,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -2098,32 +2166,32 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>J38a</t>
+          <t>CURD_0504</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>weighting*J38a</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SACANA FGS J38a "Cheese low fat and curd (unsweetened)" (Gewichtung für Curd?)</t>
+          <t>SACANA FGS J38a "Cheese low fat and curd (unsweetened)" (Only proportion of curd)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2221,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>J38</t>
+          <t>CHEESE_0505</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2168,7 +2236,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SACANA FGS J38 "Cheese n.s."</t>
+          <t>SACANA FGS J38 "Cheese n.s." + SACANA FGS J38a "Cheese low fat and curd (unsweetened)" + SACANA FGS J38b "Cheese medium fat/full fat (unsweetened)"</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2208,17 +2276,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>J39a;J38c</t>
+          <t>DAIRYDESSERT_0506</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>J39a + J38c</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2233,7 +2301,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -2263,17 +2331,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>J39c;K40b</t>
+          <t>CREAM_PROD_0507</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>J39c + K40b</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2288,7 +2356,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2386,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>J39c</t>
+          <t>DAIRYCREAM_050701</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2373,7 +2441,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>K40b</t>
+          <t>NONDAIRYCREAM_050702</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2478,22 +2546,22 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>A;L43;L45c</t>
+          <t>CEREAL_PROD_06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>A + L43 + (weighting*L45c)</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SACANA FGS A " Cereals and cereal products and starchy snacks ns" + SACANA FGS L43 "Based on Cereals ns" + (Gewichtung*SACANA FGS L45c "with vegs/potatoes/cereals")</t>
+          <t>all items for SACANA FGS A01a to A06b + SACANA FGS L43 "Based on Cereals ns" + (Proportion of SACANA FGS L45c "with vegs/potatoes/cereals")</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2503,7 +2571,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -2583,22 +2651,22 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>A04;A05;L43a;L43b</t>
+          <t>PASTA_RICE_0602</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>A04 + A05 +(weighting*L43a) + (weighting*L43b)</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SACANA FGS A04 "Pasta (any kind)" + SACANA FGS A05 " rice and other cereal grains (not ready to eat) - ns" + (Gewichtung*SACANA FGS L43a "Pasta/rice/cereals + meat/fish/eggs/cheese") + (Gewichtung*SACANA FGS L43b "Pasta/rice/cereals + legumes /vegetables/potatoes")</t>
+          <t>SACANA FGS A04 "Pasta (any kind)" + SACANA FGS A05 " rice and other cereal grains (not ready to eat) - ns" + (Proportion of SACANA FGS L43a "Pasta/rice/cereals + meat/fish/eggs/cheese") + (Proportion of SACANA FGS L43b "Pasta/rice/cereals + legumes /vegetables/potatoes")</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2608,7 +2676,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2706,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>BREAD_PROD_0603</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2653,7 +2721,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SACANA FGS A01 "bread,rolls and sim. ns"</t>
+          <t>SACANA FGS A01a " bread, crispbread, rusks, roll (refined, fiber &lt;5%)" + SACANA FGS A01b "bread, crispbread, rusks, roll (wholemeal fiber&gt;5%)"</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2693,22 +2761,22 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>A01a;A01b</t>
+          <t>BREAD_060301</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(A01a + A01b) * weighting</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SACANA FGS A01a " bread, crispbread, rusks, roll (refined, fiber &lt;5%)" + SACANA FGS A01b "bread, crispbread, rusks, roll (wholemeal fiber&gt;5%)" (Gewichtung?)</t>
+          <t>SACANA FGS A01a " bread, crispbread, rusks, roll (refined, fiber &lt;5%)" + SACANA FGS A01b "bread, crispbread, rusks, roll (wholemeal fiber&gt;5%)"</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2718,7 +2786,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -2748,22 +2816,22 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>A01a;A01b</t>
+          <t>CRISPBREAD_060302</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(A01a + A01b) * weighting</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SACANA FGS A01a " bread, crispbread, rusks, roll (refined, fiber &lt;5%)" + SACANA FGS A01b "bread, crispbread, rusks, roll (wholemeal fiber&gt;5%)" (Gewichtung?)</t>
+          <t>SACANA FGS A01a " bread, crispbread, rusks, roll (refined, fiber &lt;5%)" + SACANA FGS A01b "bread, crispbread, rusks, roll (wholemeal fiber&gt;5%)"</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2773,7 +2841,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2871,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>BREAKF_CEREALS_0604</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2818,7 +2886,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SACANA FGS A02 "breakfast cereals, corn flakes, muesli ns"</t>
+          <t>SACANA FGS A02a " complete breakfast cereals/flakes unsweetened, (sugar &lt;15%), wholemeal (fiber&gt;5%)" + SACANA FGS A02b "complete breakfast cereals/flakes sweetened (sugar&gt;15%), wholemeal (fiber&gt;5%)"</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2858,27 +2926,32 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>SALT_BISCUIT_0605</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>SACANA FGS A07 only items "Knabbergebäck" und "Kräcker"</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -2958,22 +3031,22 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>G;L42;L45b</t>
+          <t>MEAT_PROD_07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>G + L42 + (weighting* L45b)</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SACANA FGS G "Meat and meat products" + SACANA FGS L42 "based on meat" + (Gewichtung* SACANA FGS L45b "with meat/fish")</t>
+          <t>all items for SACANA FGS G29 to G33c  + (Proportion of SACANA FGS L42 "based on meat") + (Proportion of SACANA FGS L45b "with meat/fish")</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2983,7 +3056,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3086,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>G29</t>
+          <t>RED_MEAT_0701</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3028,7 +3101,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SACANA FGS G29 "meat (other than poultry)-ns"</t>
+          <t>SACANA FGS G29 "meat (other than poultry)-ns" + SACANA FGS G29a "meat - very fatty cut / fatty preparation (fat &gt;10%)" + SACANA FGS G29b "meat -low fat preparation/ lean cut and (fat &lt;10%)"</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3068,27 +3141,32 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>BEEF_070101</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>SACANA FGS G29 "meat (other than poultry)-ns" + SACANA FGS G29a "meat - very fatty cut / fatty preparation (fat &gt;10%)" + SACANA FGS G29b "meat -low fat preparation/ lean cut and (fat &lt;10%)"</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -3118,27 +3196,32 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>VEAL_070102</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SACANA FGS G29 "meat (other than poultry)-ns" + SACANA FGS G29a "meat - very fatty cut / fatty preparation (fat &gt;10%)" + SACANA FGS G29b "meat -low fat preparation/ lean cut and (fat &lt;10%)"</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -3168,27 +3251,32 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>PORK_070103</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>SACANA FGS G29 "meat (other than poultry)-ns" + SACANA FGS G29a "meat - very fatty cut / fatty preparation (fat &gt;10%)" + SACANA FGS G29b "meat -low fat preparation/ lean cut and (fat &lt;10%)"</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -3218,27 +3306,32 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>MUTTON_LAMB_070104</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>SACANA FGS G29 "meat (other than poultry)-ns" + SACANA FGS G29a "meat - very fatty cut / fatty preparation (fat &gt;10%)" + SACANA FGS G29b "meat -low fat preparation/ lean cut and (fat &lt;10%)"</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3461,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>G30</t>
+          <t>POULTRY_0702</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3383,7 +3476,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SACANA FGS G30 "poultry-ns"</t>
+          <t>SACANA FGS G30a " poultry fatty preparation (fat&gt;10%)" + SACANA FGS G30b "poultry non fatty preparation (fat&lt;10%)"</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3473,27 +3566,32 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>CHICKEN_070201</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>SACANA FGS G30a " poultry fatty preparation (fat&gt;10%)" + SACANA FGS G30b "poultry non fatty preparation (fat&lt;10%)"</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -3523,27 +3621,32 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>TURKEY_070202</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>SACANA FGS G30a " poultry fatty preparation (fat&gt;10%)" + SACANA FGS G30b "poultry non fatty preparation (fat&lt;10%)"</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -3573,27 +3676,32 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>DUCK_070203</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>SACANA FGS G30a " poultry fatty preparation (fat&gt;10%)" + SACANA FGS G30b "poultry non fatty preparation (fat&lt;10%)"</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -3673,32 +3781,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>G31</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>weighting*G31</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>SACANA FGS G31 "rabbit and game" (Gewichtung?)</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>unavailable</t>
         </is>
       </c>
     </row>
@@ -3728,32 +3831,27 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>G31</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>weighting*G32</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>SACANA FGS G31 "rabbit and game" (Gewichtung?)</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>unavailable</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3881,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>G33</t>
+          <t>PROCMEAT_0704</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3798,7 +3896,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SACANA FGS G33 " Processed meat,salami, processed poultry products , meat salad- ns"</t>
+          <t>SACANA FGS G33 " Processed meat,salami, processed poultry products , meat salad- ns" + G33a "Fatty/ very fatty items (fat &gt;20%)" + G33b "Lean/very lean items (fat &lt;20%)" + G33c "liver, blood and derived processed meats"</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3838,7 +3936,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>G32</t>
+          <t>OFFALS_0705</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3893,22 +3991,22 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>H;L45b;L46</t>
+          <t>FISH_SHELLFISH_08</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>H + (weighting*L45b) + (weighting*L46)</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SACANA FGS H"Finfish, shelfish and their products" + (Gewichtung*SACANA FGS L45b "with meat/fish") + (Gewichtung*SACANA FGS L46 "Based on fish")</t>
+          <t>all items from H34" Fish and seafood" + H34a "Fish, fatty preparation" + H34b "Fish, lean preparation" + H35 "Processed fish products"</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3918,7 +4016,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -3948,32 +4046,32 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>H34</t>
+          <t>FISH_0801</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>weighting*H34</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SACANA FGS H34 "Fish and seafood" (Gewichtung?)</t>
+          <t>SACANA FGS H34 "Fish and seafood" + SACANA FGS H34a + SACANA FGS H34b</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -4003,32 +4101,32 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>H34</t>
+          <t>CRUSTACEANS_0802</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>weighting*H34</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SACANA FGS H34 "Fish and seafood" (Gewichtung?)</t>
+          <t>SACANA FGS H34 "Fish and seafood" + SACANA FGS H34a + SACANA FGS H34b</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4156,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>H35</t>
+          <t>FISH_PROD_0803</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4113,22 +4211,22 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>I;L45</t>
+          <t>EGG_PROD_09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>I+ (weighting*L45)</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SACANA FGS I "Eggs" + (Gewichtung*L45 "based on eggs")</t>
+          <t>SACANA FGS I36 " eggs and simple egg recipes (not fried)" + I37 "eggs and simple egg recipes (fried, stirfried)"</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4138,7 +4236,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -4168,32 +4266,27 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>SACANA FGS I "Eggs"</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>identical</t>
+          <t>unavailable</t>
         </is>
       </c>
     </row>
@@ -4223,22 +4316,22 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C12;C13;C14</t>
+          <t>FAT_10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>C12 + C13 + C14</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SACANA FGS C12 "vegetable oils ns" + SACANA FGS C13 "margarines and lipids of mixed origin" + SACANA FGS C14 "butter and animal fats"</t>
+          <t>SACANA FGS C12 "vegetable oils ns" + C12a "olive oil" + C12b " other vegetable oils" + C13 "margarines and lipids of mixed origin" + C14 "butter and animal fats"</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4248,7 +4341,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4371,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C12</t>
+          <t>VEGOILS_1001</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4293,7 +4386,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>SACANA FGS C12 "vegetable oils ns"</t>
+          <t>SACANA FGS C12 "vegetable oils + C12a "olive oil" + C12b " other vegetable oils"</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4333,32 +4426,32 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C14</t>
+          <t>BUTTER_1002</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>weighting*C14</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>SACANA FGS C14 "butter and animal fats" (Gewichtung für Butter?)</t>
+          <t>SACANA FGS C14 "butter and animal fats"</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4481,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>MARGARINE_1003</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4543,32 +4636,27 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>C14</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>weighting*C14</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>SACANA FGS C14 "butter and animal fats" (Gewichtung für animal fat?)</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>unavailable</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4686,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SUGAR_CONFECT_11</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4613,7 +4701,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SACANA FGS B "Sugar and sugar products"</t>
+          <t>SACANA FGS B08 "Sugar, honey, jam and sweet sauces or dessert sauces " + B09 "Confectionery (non chocolate)" + B09b "Candies, candy bars, chewing gum, (with sugar)" + B10a "chocolate bars , chocolate coated nuts, confetti, twix, lion, mars" + B10b "chocolate spread, paste, powder, sauce" + B11 " Other sugar product - ns" + B11a "marzipan, sugar coated peanuts/almonds. nutspread" + B11b "water ice, sorbet (excluding ice cream)"</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4653,7 +4741,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>B08</t>
+          <t>HONEY_JAM_1101</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4708,7 +4796,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>B10</t>
+          <t>CHOCOLATE_1102</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4723,7 +4811,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SACANA FGS B10 "Chocolate ns"</t>
+          <t>SACANA FGS B10a "chocolate bars , chocolate coated nuts, confetti, twix, lion, mars" + B10b "chocolate spread, paste, powder, sauce"</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4763,7 +4851,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>B09</t>
+          <t>NONCHOC_SWEETS_1103</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4778,7 +4866,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SACANA FGS B09 "Confectionery (non chocolate)"</t>
+          <t>SACANA FGS B09 "Confectionery (non chocolate)" + B09b "Candies, candy bars, chewing gum, (with sugar)</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4868,27 +4956,32 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>ICECREAM_1105</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>SACANA FGS J39a "milk based ice-creams, desserts, (chocolate) pudding" (only Milcheis) + B11b "water ice, sorbet (excluding ice cream)"</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -4918,32 +5011,32 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>J39a</t>
+          <t>ICECREAM_MILK_110501</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>weighting*J39a</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>SACANA FGS J39a "milk based ice-creams, desserts, (chocolate) pudding" (Gewichtung für Milcheis?)</t>
+          <t>SACANA FGS J39a "milk based ice-creams, desserts, (chocolate) pudding" (Proportion of Milcheis)</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -4973,32 +5066,32 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>B11b</t>
+          <t>SORBET_110502</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>weighting*B11b</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>SACANA FGS B11b "water ice, sorbet (excluding ice cream)" (Gewichtung für Sorbet?)</t>
+          <t>SACANA FGS B11b "water ice, sorbet (excluding ice cream)" (Proportion of Sorbet)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -5028,32 +5121,32 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>B11b</t>
+          <t>WATER_ICE_110503</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>weighting*B11b</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SACANA FGS B11b "water ice, sorbet (excluding ice cream)" (Gewichtung für Wassereis?)</t>
+          <t>SACANA FGS B11b "water ice, sorbet (excluding ice cream)" (Proportion of Wassereis)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>tentative</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5176,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>CAKES_12</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5098,7 +5191,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>SACANA FGS A06 " Sweet bakery, biscuits, pies (sweet), cakes , sweet fritters and other confectionery"</t>
+          <t>SACANA FGS A06 "Sweet bakery, biscuits, pies (sweet), cakes , sweet fritters and other confectionery" + A06a "(fat &gt;20%)" + A06b "(fat &lt;20%)"</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5238,22 +5331,22 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>E22;E23;E24;E25</t>
+          <t>NONALC_BEV_13</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>E22 + E23 + E24 + E25</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SACANA FGS E22 "water" + SACANA FGS E23 "coffee, tea, coffee surrogate, decafe, herbal - ns" + SACANA FGS E24 "fruit, vegetable juices and smoothies - ns" + SACANA FGS E25 "Soft and sweetened drinks"</t>
+          <t>SACANA FGS E22 "water" + E23 "coffee, tea, coffee surrogate, decafe, herbal - ns" + E24 "fruit, vegetable juices and smoothies - ns" + E24b "fruit (and vegetable) juices - manufactured" + E25 "Soft and sweetened drinks" + E25a "carbonated drink (sweetened )" + E25b "carbonated drink (low calory, reduced sugar)" + E25c "other drinks normally sweetened"</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5263,7 +5356,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5386,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>FRUITVEG_JUICE_1301</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5308,7 +5401,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SACANA FGS E24 "fruit, vegetable juices and smoothies - ns"</t>
+          <t>SACANA FGS E24 "fruit, vegetable juices and smoothies - ns" + E24b "fruit (and vegetable) juices - manufactured"</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5348,7 +5441,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>E25</t>
+          <t>SOFTDRINKS_1302</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5363,7 +5456,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SACANA FGS E25 "Soft and sweetened drinks"</t>
+          <t>SACANA FGS E25a "carbonated drink (sweetened )" + E25b "carbonated drink (low calory, reduced sugar")</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5403,7 +5496,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>E23</t>
+          <t>HOTDRINKS_1303</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5458,27 +5551,32 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>COFFEE_130301</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>SACANA FGS E23 "coffee, tea, coffee surrogate, decafe, herbal - ns" (Proportion Kaffee?)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -5508,27 +5606,32 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>TEA_130302</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>SACANA FGS E23 "coffee, tea, coffee surrogate, decafe, herbal - ns"  (Proportion Tee (grün und schwarz)?)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -5558,27 +5661,32 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>HERBALTEA_130303</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>SACANA FGS E23 "coffee, tea, coffee surrogate, decafe, herbal - ns" (Proportion Tee (Früchte und Kräuter)?)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -5608,27 +5716,32 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>COFFEE_IMITATE_130304</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>SACANA FGS E23 "coffee, tea, coffee surrogate, decafe, herbal - ns" (Proportion Malzkaffee?)</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5771,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>E22</t>
+          <t>WATER_1304</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5713,32 +5826,27 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>SACANA FGS F "Alcoholic beverages ns"</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>identical</t>
+          <t>unavailable</t>
         </is>
       </c>
     </row>
@@ -5768,32 +5876,27 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>F27</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>SACANA FGS F27 "Wine"</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>identical</t>
+          <t>unavailable</t>
         </is>
       </c>
     </row>
@@ -5873,32 +5976,27 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>F26</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>direct_mapping</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>SACANA FGS F26 "Beer and cider"</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>identical</t>
+          <t>unavailable</t>
         </is>
       </c>
     </row>
@@ -6128,7 +6226,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>C15</t>
+          <t>CONDIMENT_SAUCES_15</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6143,7 +6241,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>SACANA FGS C15 Sauces, dressing and condiments - ns</t>
+          <t>SACANA FGS C15 "Sauces, dressing and condiments - ns" + C15a "Cold sauces &gt;40% fat" + C15b "Cold sauces &lt;40% fat" + C15c "Very Low/no calory condiments and other minor ingredients" + C15d "Based on meat" + C15e "Based on vegetables" + C15f "Based on dairy" + C15h "Based on meat, cheese, eggs, vegs"</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6183,27 +6281,32 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>SAUCES_1501</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>SACANA FGS C15 "Sauces, dressing and condiments - ns" + C15a "Cold sauces &gt;40% fat" + C15b "Cold sauces &lt;40% fat" + C15c "Very Low/no calory condiments and other minor ingredients" + C15d "Based on meat" + C15e "Based on vegetables" + C15f "Based on dairy" + C15h "Based on meat, cheese, eggs, vegs" minus herbs, spices and condiments</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -6233,27 +6336,32 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>TOMATOSAUCE_150101</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>SACANA FGS C15e (Proportion Tomatensoße)</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -6283,27 +6391,32 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>DRESSINGS_150102</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>SACANA FGS C15a "Cold sauces &gt;40% fat" + C15b "Cold sauces &lt;40% fat" + C15f "Based on dairy" (Proportion  Dressings?)</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -6333,27 +6446,32 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>MAYONNAISE_150103</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>SACANA FGS C15a "Cold sauces &gt;40% fat" (Proportion Mayonnaise?)</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -6383,27 +6501,32 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>DESSERTSAUCE_150104</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>SACANA FGS C15c "Very Low/no calory condiments and other minor ingredients" (Proportion Fruchtsoße?)</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -6483,27 +6606,32 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>HERBS_SPICES_1503</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>SACANA FGS C15c "Very Low/no calory condiments and other minor ingredients" (Proportion Herbs, Spices?)</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -6533,27 +6661,32 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>CONDIMENTS_1504</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>SACANA FGS C15a "Cold sauces &gt;40% fat" + C15b "Cold sauces &lt;40% fat" (Proportion Condiments?)</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -6583,22 +6716,22 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>E21;L44a;L44b</t>
+          <t>SOUP_BOUILLON_16</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>E21 + L44a + L44b</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>SACANA FGS E21 " Bouillon - meat/fish/vegetable" + SACANA FGS L44a "Soup, veloutè, LIQUID" + SACANA FGS L44b "Soup, veloutè, NOT LIQUID"</t>
+          <t>SACANA FGS E21 " Bouillon - meat/fish/vegetable" + SACANA FGS L44a "Soup, veloutè, LIQUID" + SACANA FGS L44b "Soup, veloutè, NOT LIQUID" (Proportion Suppen, Eintöpfe?)</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -6608,7 +6741,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -6638,27 +6771,32 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>SOUP_1601</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>SACANA FGS L44a "Soup, veloutè, LIQUID"</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -6688,27 +6826,32 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>BOUILLON_1602</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>SACANA FGS E21 " Bouillon - meat/fish/vegetable"</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -6738,27 +6881,32 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>MISCELLANEOUS_17</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>SACANA FGS K40a "Vegetarian burgers, tempeh, tofu, seitan" + K40c "Soy based dessert, cakes,and similar"</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6936,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>K40a</t>
+          <t>VEG_DISHES_1700</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -6843,7 +6991,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>K40c</t>
+          <t>SOY_PROD_1701</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -6898,27 +7046,27 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>DIET_PROD_1702</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7246,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>_BLANK_</t>
+          <t>__BLANK__</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">

--- a/rmonize/data_proc_elem/DPE_IDEFICS_P1.xlsx
+++ b/rmonize/data_proc_elem/DPE_IDEFICS_P1.xlsx
@@ -497,10 +497,10 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>case_when(_x000D_
-  sex_child == 1 ~ 1L, _x000D_
-  sex_child == 2 ~ 2L, _x000D_
-  TRUE ~ NA_integer__x000D_
+          <t>case_when(_x000D__x000D_
+  sex_child == 1 ~ 1L, _x000D__x000D_
+  sex_child == 2 ~ 2L, _x000D__x000D_
+  TRUE ~ NA_integer__x000D__x000D_
 )</t>
         </is>
       </c>
@@ -616,12 +616,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>proximate</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>phys_activ;leis_activ</t>
+          <t>phys_activ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -661,22 +661,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.17 * (phys_activ + leis_activ) / 7</t>
+          <t>6.0 * phys_activ / 7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>The average MET value of children between 6 to 15years was determined according to NCCOR Compendium.METy Values (Smoothed) – View All Categories - NCCOR Youth Compendium of Physical Activities</t>
+          <t>The average MET value of children between 6 to 15years was determined according to NCCOR Compendium.METy Values (Smoothed) – View All Categories - NCCOR Youth Compendium of Physical Activities; FS-TOB: formula changed to reflect children ages 6-9 and reduce overlap (dropping leis_activ)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>compatible</t>
+          <t>proximate</t>
         </is>
       </c>
     </row>
